--- a/EstablecimientoSalud/excels/LA_LIBERTAD-TRUJILLO-TRUJILLO.xlsx
+++ b/EstablecimientoSalud/excels/LA_LIBERTAD-TRUJILLO-TRUJILLO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -493,7 +493,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>21178</t>
+          <t>21228</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -518,27 +518,27 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-8.1090524</t>
+          <t>-8.09018343</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-79.0215336</t>
+          <t>-79.00239931</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>DERMATOLOGIA CLINICA ALEGRE</t>
+          <t>CENTRO DE SALUD MENTAL COMUNITARIA TRUJILLO DRA. FRIDA ALAYZA COSSAO</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>AVENIDA AV METROPOLITANA/ II /MZ E 1/ L 8 /SAN ISIDRO DISTRITO TRUJILLO PROVINCIA TRUJILLO DEPARTAMENTO LA LIBERTAD</t>
+          <t>AVENIDA CESAR VALLEJO/ MZ 45 AA. HH. HUERTA BELLA NUMERO S/N DISTRITO TRUJILLO PROVINCIA TRUJILLO DEPARTAMENTO LA LIBERTAD</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>I-2</t>
+          <t>I-3</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -555,7 +555,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>31122</t>
+          <t>32053</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -580,32 +580,32 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-8.099167</t>
+          <t>-8.0947692</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-79.03700714</t>
+          <t>-79.0218325</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>POLICLINICO HORIZONTE MEDIC</t>
+          <t>CENTRO DE SALUD EJERCITO PERUANO</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>AVENIDA NICOLAS DE PIEROLA NUMERO 1106 URBANIZACION SAN FERNANDO DISTRITO TRUJILLO PROVINCIA TRUJILLO DEPARTAMENTO LA LIBERTAD</t>
+          <t>AVENIDA AMERICA S/N URBANIZACION PAY PAY DISTRITO TRUJILLO PROVINCIA TRUJILLO DEPARTAMENTO LA LIBERTAD</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>I-3</t>
+          <t>I-4</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -617,7 +617,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>21228</t>
+          <t>26446</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -642,22 +642,22 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-8.09018343</t>
+          <t>-8.1090524</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-79.00239931</t>
+          <t>-79.0215336</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD MENTAL COMUNITARIA TRUJILLO DRA. FRIDA ALAYZA COSSAO</t>
+          <t>CENTRO DE SALUD MENTAL COMUNITARIO SEMBRANDO ESPERANZA DE HUAMACHUCO</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>AVENIDA CESAR VALLEJO/ MZ 45 AA. HH. HUERTA BELLA NUMERO S/N DISTRITO TRUJILLO PROVINCIA TRUJILLO DEPARTAMENTO LA LIBERTAD</t>
+          <t>SUAREZ 1145 AL COSTADO DEL TERMINAL DE MARCABALITO,FRENTE AL ESTADIO MUNICIPAL(PASAJE HOSPITAL) HUAMACHUCO SANCHEZ CARRION LA LIBERTAD</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,7 +679,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>15215</t>
+          <t>5198</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -704,22 +704,22 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-8.11273143</t>
+          <t>-8.12384639</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-79.03058874</t>
+          <t>-79.02618409</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>POLICLINICO SEAOR DE LOS MILAGROS</t>
+          <t>SAN MARTIN DE PORRES</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>JR. FRANCISCO BOLOGNESI 382-386. CENTRO CAVICO DISTRITO TRUJILLO PROVINCIA TRUJILLO DEPARTAMENTO LA LIBERTAD</t>
+          <t>OTROS MZ. O LOTE 1 - LOZ JAZMINES DISTRITO TRUJILLO PROVINCIA TRUJILLO DEPARTAMENTO LA LIBERTAD</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -741,7 +741,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>32053</t>
+          <t>5202</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -766,22 +766,22 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-8.0947692</t>
+          <t>-8.11303099</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-79.0218325</t>
+          <t>-79.0071627</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD EJERCITO PERUANO</t>
+          <t>EL BOSQUE</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>AVENIDA AMERICA S/N URBANIZACION PAY PAY DISTRITO TRUJILLO PROVINCIA TRUJILLO DEPARTAMENTO LA LIBERTAD</t>
+          <t>CALLE CALLE JULIA CODESIDO Nº 1082 DISTRITO TRUJILLO PROVINCIA TRUJILLO DEPARTAMENTO LA LIBERTAD</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -803,7 +803,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>36656</t>
+          <t>5206</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -828,22 +828,22 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-8.1194649</t>
+          <t>-8.09085289</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-79.0372734</t>
+          <t>-78.99467568</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>COA - CENTRO ODONTOLOGICO AMERICANO</t>
+          <t>LIBERTAD</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>PASAJE SAN MARTIN DE PORRES NUMERO 230 URBANIZACION SAN ANDRES II ETAPA DISTRITO TRUJILLO PROVINCIA TRUJILLO DEPARTAMENTO LA LIBERTAD</t>
+          <t>OTROS MZ I LOTE 1 - URB LIBERTAD DISTRITO TRUJILLO PROVINCIA TRUJILLO DEPARTAMENTO LA LIBERTAD</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -865,7 +865,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>13765</t>
+          <t>11154</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,22 +890,22 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-8.089447</t>
+          <t>-8.1060428</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-79.0237771</t>
+          <t>-79.0329727</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>POLICLINICO SAN JOSEMARIA</t>
+          <t>SANIDAD DE LA PNP - TRUJILLO</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>OTROS LOS LAURELES 808 DISTRITO FLORENCIA DE MORA PROVINCIA TRUJILLO DEPARTAMENTO LA LIBERTAD</t>
+          <t>AVENIDA AV. SANTA TERESITA DE JESUS S/N URB.  MONSERRATE NUMERO S/N DISTRITO TRUJILLO PROVINCIA TRUJILLO DEPARTAMENTO LA LIBERTAD</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -927,7 +927,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>26641</t>
+          <t>5207</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -952,27 +952,27 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-8.1160962</t>
+          <t>-8.09879639</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-79.0239778</t>
+          <t>-79.00114805</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>MEDICENTRO TRUJILLO</t>
+          <t>PESQUEDA III</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>CALLE LLOQUE YUPANQUI NUMERO 273 URBANIZACION SANTA MARIA DISTRITO TRUJILLO PROVINCIA TRUJILLO DEPARTAMENTO LA LIBERTAD</t>
+          <t>AVENIDA AVENIDA 5 DE ABRIL MZ 4 LOTE 22 DISTRITO TRUJILLO PROVINCIA TRUJILLO DEPARTAMENTO LA LIBERTAD</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>I-3</t>
+          <t>I-2</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -989,7 +989,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>26446</t>
+          <t>31725</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1014,35 +1014,345 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-8.1090524</t>
+          <t>-8.1070395</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-79.0215336</t>
+          <t>-79.0255994</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>CENTRO DE SALUD MENTAL COMUNITARIO SEMBRANDO ESPERANZA DE HUAMACHUCO</t>
+          <t>CLUB DE LEONES</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>SUAREZ 1145 AL COSTADO DEL TERMINAL DE MARCABALITO,FRENTE AL ESTADIO MUNICIPAL(PASAJE HOSPITAL) HUAMACHUCO SANCHEZ CARRION LA LIBERTAD</t>
+          <t>INDEPENDENCIA NUMERO 839 DISTRITO TRUJILLO PROVINCIA TRUJILLO DEPARTAMENTO LA LIBERTAD</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
+          <t>I-2</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>130101</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>35741</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>130101</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>-8.1042174</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-79.0089785</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>CAP III METROPOLITANO</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>AVENIDA BLAS PASCAL NUMERO 268 URBANIZACION LA NORIA DISTRITO TRUJILLO PROVINCIA TRUJILLO DEPARTAMENTO LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>I-3</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>130101</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>5203</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>130101</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>-8.09495116</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-79.01337229</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>LOS GRANADOS "SAGRADO CORAZON"</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>AVENIDA AVENIDA FEDERICO VILLARREAL 301 - URB LOS GRANADOS DISTRITO TRUJILLO PROVINCIA TRUJILLO DEPARTAMENTO LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>I-4</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>130101</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>5199</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>130101</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>-8.1002909</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-79.01726399</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>LA UNION</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>AVENIDA AVENIDA SANTA Nº 1021-EL MOLINO DISTRITO TRUJILLO PROVINCIA TRUJILLO DEPARTAMENTO LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>I-3</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>130101</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>5200</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>130101</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>-8.0944571</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-79.02087539</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>LOS JARDINES</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>JIRON PAZ SOLDAN Nº 220 URBANIZACION LOS JARDINES DISTRITO TRUJILLO PROVINCIA TRUJILLO DEPARTAMENTO LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>I-3</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>130101</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>5201</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>130101</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>-8.10482228</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-79.01385</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>ARANJUEZ</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>JIRON CHICLAYO Nº 108 DISTRITO TRUJILLO PROVINCIA TRUJILLO DEPARTAMENTO LA LIBERTAD</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>I-3</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
         <is>
           <t>130101</t>
         </is>

--- a/EstablecimientoSalud/excels/LA_LIBERTAD-TRUJILLO-TRUJILLO.xlsx
+++ b/EstablecimientoSalud/excels/LA_LIBERTAD-TRUJILLO-TRUJILLO.xlsx
@@ -425,35 +425,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>ubigeo_gestor</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>PROVINCIA</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>DISTRITO</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Codigo_Unico</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>UBIGEO</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>DEPARTAMENTO</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>PROVINCIA</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>DISTRITO</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>LATITUD</t>
@@ -482,40 +482,35 @@
       <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Siniestros_fatales</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>ubigeo_gestor</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>130101</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>21228</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>130101</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>-8.09018343</t>
@@ -544,40 +539,35 @@
       <c r="K2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>130101</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>130101</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>32053</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>130101</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>-8.0947692</t>
@@ -606,40 +596,35 @@
       <c r="K3" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>130101</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>130101</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>26446</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>130101</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>-8.1090524</t>
@@ -668,40 +653,35 @@
       <c r="K4" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>130101</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>130101</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>5198</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>130101</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>-8.12384639</t>
@@ -730,40 +710,35 @@
       <c r="K5" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>130101</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>130101</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>5202</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>130101</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>-8.11303099</t>
@@ -792,40 +767,35 @@
       <c r="K6" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>130101</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>130101</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>5206</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>130101</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>-8.09085289</t>
@@ -854,40 +824,35 @@
       <c r="K7" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>130101</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>130101</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>11154</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>130101</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>-8.1060428</t>
@@ -916,40 +881,35 @@
       <c r="K8" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>130101</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>130101</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>5207</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>130101</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>-8.09879639</t>
@@ -978,40 +938,35 @@
       <c r="K9" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>130101</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>130101</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>31725</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>130101</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>-8.1070395</t>
@@ -1040,40 +995,35 @@
       <c r="K10" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>130101</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>130101</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>35741</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>130101</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>-8.1042174</t>
@@ -1102,40 +1052,35 @@
       <c r="K11" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>130101</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>130101</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>5203</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>130101</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>-8.09495116</t>
@@ -1164,40 +1109,35 @@
       <c r="K12" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>130101</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>130101</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>5199</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>130101</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>-8.1002909</t>
@@ -1226,40 +1166,35 @@
       <c r="K13" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>130101</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>130101</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>5200</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>130101</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>-8.0944571</t>
@@ -1288,40 +1223,35 @@
       <c r="K14" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>130101</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>130101</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>LA_LIBERTAD</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>TRUJILLO</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>5201</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>130101</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>LA LIBERTAD</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>TRUJILLO</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>-8.10482228</t>
@@ -1350,11 +1280,6 @@
       <c r="K15" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>130101</t>
         </is>
       </c>
     </row>

--- a/EstablecimientoSalud/excels/LA_LIBERTAD-TRUJILLO-TRUJILLO.xlsx
+++ b/EstablecimientoSalud/excels/LA_LIBERTAD-TRUJILLO-TRUJILLO.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Codigo_Unico</t>
+          <t>Codigo</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">

--- a/EstablecimientoSalud/excels/LA_LIBERTAD-TRUJILLO-TRUJILLO.xlsx
+++ b/EstablecimientoSalud/excels/LA_LIBERTAD-TRUJILLO-TRUJILLO.xlsx
@@ -493,7 +493,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -550,7 +550,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -721,7 +721,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -835,7 +835,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1063,7 +1063,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1234,7 +1234,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LA_LIBERTAD</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
